--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_biobio_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_biobio_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:11</t>
+    <t xml:space="preserve">2026-09-29 14:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_biobio_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_biobio_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:08</t>
+    <t xml:space="preserve">2026-09-29 18:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -504,10 +504,10 @@
         <v>1.29</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>30.31</v>
+        <v>30.32</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>29.02</v>
+        <v>29.03</v>
       </c>
     </row>
     <row r="4">
@@ -518,10 +518,10 @@
         <v>-3.61</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>22.35</v>
+        <v>22.34</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>25.96</v>
+        <v>25.95</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_biobio_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_biobio_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:38</t>
+    <t xml:space="preserve">2026-10-05 04:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -518,10 +518,10 @@
         <v>-3.61</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>22.34</v>
+        <v>22.35</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>25.95</v>
+        <v>25.96</v>
       </c>
     </row>
   </sheetData>
